--- a/results/Int Task Remove ACC -0.0/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_2_permute.xlsx
@@ -440,427 +440,427 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7357258362437094</v>
+        <v>0.7489789721880797</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7165624357288579</v>
+        <v>0.7489789721880797</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7192609708098139</v>
+        <v>0.7463952113551939</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7196464758213791</v>
+        <v>0.7503962270220006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7393696140173716</v>
+        <v>0.7477288832441296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7397551190289368</v>
+        <v>0.7477288832441296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7397239277258518</v>
+        <v>0.7537622072525628</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7363862146137103</v>
+        <v>0.7515115597893418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7317672212545336</v>
+        <v>0.7609720282242304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7316595137860686</v>
+        <v>0.7609720282242304</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7322151088722687</v>
+        <v>0.7612568925469356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7322845582580437</v>
+        <v>0.7587667056233045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7322845582580437</v>
+        <v>0.7558598223850235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7195628928763937</v>
+        <v>0.7533625686817873</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7201950041279741</v>
+        <v>0.7581728524544145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7362967832993965</v>
+        <v>0.7616211972196852</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7372761414798519</v>
+        <v>0.7570957777697633</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7366199057047919</v>
+        <v>0.7643721239425417</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7323793505775752</v>
+        <v>0.7642644164740766</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7240824639569872</v>
+        <v>0.7528622894221519</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7256486085267275</v>
+        <v>0.7569398212543388</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7256486085267275</v>
+        <v>0.7631291017781967</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7276073248876382</v>
+        <v>0.7744305881412614</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7231684125673659</v>
+        <v>0.7631602930812816</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.671707392436304</v>
+        <v>0.7558910136881084</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6158586332165934</v>
+        <v>0.7561305531485184</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6189426733091146</v>
+        <v>0.7664456145515227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6194046944860599</v>
+        <v>0.7289285689917508</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6348178281690607</v>
+        <v>0.7494239356211505</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6352033331806259</v>
+        <v>0.7254602422979413</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.627531491032013</v>
+        <v>0.7251612444160257</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5817753114987714</v>
+        <v>0.7274360164027265</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.542832238551086</v>
+        <v>0.6779824490436455</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.542832238551086</v>
+        <v>0.6688239026753365</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5515670218251396</v>
+        <v>0.6196880967164331</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.545461324246267</v>
+        <v>0.5964530127387231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5303359790706357</v>
+        <v>0.596067507727158</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5420924198310406</v>
+        <v>0.598318155190379</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5135650489752195</v>
+        <v>0.5964018395070995</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5272278144546347</v>
+        <v>0.6022609308459569</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5232026742643483</v>
+        <v>0.5864693589309961</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5372026957083691</v>
+        <v>0.6369446851481636</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5428151808072114</v>
+        <v>0.6750031922349251</v>
       </c>
     </row>
     <row r="45">
@@ -870,397 +870,397 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5222133251196236</v>
+        <v>0.6889125639543554</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5211262594707031</v>
+        <v>0.6740508827626137</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5227377289027387</v>
+        <v>0.6759925413796499</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5336707679981129</v>
+        <v>0.6882110033170001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5345806767927933</v>
+        <v>0.7281517105992921</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5349661818043584</v>
+        <v>0.7254531755183361</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5479968360321933</v>
+        <v>0.5954285733780279</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.541387935009021</v>
+        <v>0.6018744511061703</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5244257145001545</v>
+        <v>0.5499107148949194</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5228142450681189</v>
+        <v>0.551522184326955</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5225676388281038</v>
+        <v>0.5352473908962334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5225676388281038</v>
+        <v>0.5334304974915369</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5201157099871628</v>
+        <v>0.5285578311127399</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5197302049755977</v>
+        <v>0.5273942492984394</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5224287400565537</v>
+        <v>0.5416338102028702</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5212722250218583</v>
+        <v>0.4941601595435153</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5120201047442947</v>
+        <v>0.5172151624823209</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5120201047442947</v>
+        <v>0.524025344883213</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5104780846980341</v>
+        <v>0.519438761237398</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5117040491185045</v>
+        <v>0.5110582916718246</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5117040491185045</v>
+        <v>0.5063345150288471</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5117040491185045</v>
+        <v>0.5063345150288471</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5023824794551659</v>
+        <v>0.4636440994339753</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5023824794551659</v>
+        <v>0.4723235668814643</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5046955095245569</v>
+        <v>0.4710593443783038</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5039244995014265</v>
+        <v>0.4778795177434652</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5077795496170781</v>
+        <v>0.4651096033148557</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5073245952197378</v>
+        <v>0.4458343527365982</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5073245952197378</v>
+        <v>0.4449797597684825</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5069390902081727</v>
+        <v>0.4701635691428337</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5007710100231303</v>
+        <v>0.4781755914407165</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4999617419173099</v>
+        <v>0.4781755914407165</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4992601812799546</v>
+        <v>0.4781755914407165</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.497995958776794</v>
+        <v>0.4382689996461737</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4957835693962631</v>
+        <v>0.429843205218305</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4981348575483441</v>
+        <v>0.4220948469043119</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4930397094530118</v>
+        <v>0.4063473814413696</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4945746627196672</v>
+        <v>0.4422753763181981</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4944810888104125</v>
+        <v>0.4598256016266265</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4941650331846223</v>
+        <v>0.4608885427520672</v>
       </c>
     </row>
     <row r="85">
@@ -1270,57 +1270,57 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4941650331846223</v>
+        <v>0.4608885427520672</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4971172412851986</v>
+        <v>0.4686510346252706</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4970095338167336</v>
+        <v>0.4999858664407896</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4972561400567487</v>
+        <v>0.4999858664407896</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.500069449385775</v>
+        <v>0.4989370588745593</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4997533937599848</v>
+        <v>0.4985132957803041</v>
       </c>
     </row>
   </sheetData>
